--- a/output/pdf_financials_xlsx/RK.xlsx
+++ b/output/pdf_financials_xlsx/RK.xlsx
@@ -5662,13 +5662,13 @@
         <v>0.743785</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.966735</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.956277</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.015739</v>
       </c>
     </row>
     <row r="93">
@@ -7018,43 +7018,43 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-7.45655</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.612802</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-4.525739</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-2.958077</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-3.747078</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.758776</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.722688</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-4.35803</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-3.745442</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.135287</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.506367</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.258064</v>
       </c>
     </row>
     <row r="119">
@@ -9322,7 +9322,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -32872,7 +32876,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RK.xlsx
+++ b/output/pdf_financials_xlsx/RK.xlsx
@@ -1005,52 +1005,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.025779</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004166</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.09543</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.07419099999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019187</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.018715</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.017676</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003253</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.015729</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.008940999999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.02426</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001275</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.059062</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.051722</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.024457</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.02515</v>
       </c>
     </row>
     <row r="13">
@@ -1952,22 +1952,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.474311</v>
+        <v>-4.50009</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.528244</v>
+        <v>-0.53241</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.046181</v>
+        <v>-1.141611</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.256027</v>
+        <v>-3.330218</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.544752</v>
+        <v>-3.563939</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.08587400000000001</v>
+        <v>-0.104589</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1975,31 +1975,31 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.8833</v>
+        <v>-0.886553</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.585406</v>
+        <v>-0.601135</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.784583</v>
+        <v>-0.793524</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.618456</v>
+        <v>-0.642716</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.104697</v>
+        <v>-1.105972</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.342733</v>
+        <v>-1.401795</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.006332</v>
+        <v>-1.058054</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.514078</v>
+        <v>-0.538535</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.280438</v>
+        <v>-1.305588</v>
       </c>
     </row>
     <row r="28">
@@ -2064,22 +2064,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.474311</v>
+        <v>-4.50009</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.528244</v>
+        <v>-0.53241</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.046181</v>
+        <v>-1.141611</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.256027</v>
+        <v>-3.330218</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.544752</v>
+        <v>-3.563939</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.08587400000000001</v>
+        <v>-0.104589</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.8833</v>
+        <v>-0.886553</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.585406</v>
+        <v>-0.601135</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.784583</v>
+        <v>-0.793524</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.618456</v>
+        <v>-0.642716</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.104697</v>
+        <v>-1.105972</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.342733</v>
+        <v>-1.401795</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.006332</v>
+        <v>-1.058054</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.514078</v>
+        <v>-0.538535</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.280438</v>
+        <v>-1.305588</v>
       </c>
     </row>
     <row r="30">
@@ -2380,7 +2380,7 @@
         <v>0.543542</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.163015</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>1.103107</v>
@@ -2490,7 +2490,7 @@
         <v>0.601762</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.110667</v>
+        <v>1.273682</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1.183341</v>
@@ -3150,7 +3150,7 @@
         <v>0.215553</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.221908</v>
+        <v>0.058893</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.059841</v>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -48536,7 +48536,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" s="5" t="n">
@@ -52052,7 +52052,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -53690,7 +53690,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -56492,7 +56492,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">

--- a/output/pdf_financials_xlsx/RK.xlsx
+++ b/output/pdf_financials_xlsx/RK.xlsx
@@ -1291,7 +1291,7 @@
         <v>0.6691780000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.42694</v>
+        <v>0.42694</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-1.047117</v>
@@ -1300,7 +1300,7 @@
         <v>0.167497</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.09857200000000001</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.06801400000000001</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.5349739999999999</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.142498</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -32132,7 +32132,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -33972,7 +33976,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -34250,7 +34258,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -35088,7 +35100,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -36516,7 +36532,11 @@
           <t>Deferred income tax expense (recovery) 68,014</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -37088,7 +37108,11 @@
           <t>Proceeds on sale of marketable securities -</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -40254,7 +40278,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -41302,7 +41330,11 @@
           <t>Deferred income tax expense 426,940</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -42844,7 +42876,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E373" s="5" t="n">
         <v>-0.801154</v>
       </c>
@@ -49906,7 +49942,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -50082,7 +50122,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -53980,7 +54024,11 @@
           <t>Deferred income tax recovery 10 19,529</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -58324,7 +58372,11 @@
           <t>Future income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -59754,7 +59806,11 @@
           <t>Future income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E553" s="5" t="n">
         <v>0.801154</v>
       </c>
